--- a/cypress/fixtures/Central IKON_PIS_Latest_version.xlsx
+++ b/cypress/fixtures/Central IKON_PIS_Latest_version.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RamaShashank\Desktop\SIPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C69147D-7635-4B9E-AEE0-BAC9BAD2641A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14BC3B0E-1F9D-4B22-A8BD-249C483216FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3840" yWindow="3990" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Info Sheet" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="175">
   <si>
     <t>PROJECT INFORMATION SHEET</t>
   </si>
@@ -356,9 +356,6 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>Central IKON</t>
-  </si>
-  <si>
     <t>Shankar Fenestrations &amp; Glasses India Private Limited</t>
   </si>
   <si>
@@ -371,9 +368,6 @@
     <t>Received</t>
   </si>
   <si>
-    <t>May,2027</t>
-  </si>
-  <si>
     <t>NA</t>
   </si>
   <si>
@@ -395,9 +389,6 @@
     <t>SECTOR-105 | NOIDA</t>
   </si>
   <si>
-    <t>Rs. 5,42,44,634</t>
-  </si>
-  <si>
     <t>5,06,92,723</t>
   </si>
   <si>
@@ -530,9 +521,6 @@
     <t>Fabricator for designs</t>
   </si>
   <si>
-    <t>June,2027</t>
-  </si>
-  <si>
     <t>remaks….</t>
   </si>
   <si>
@@ -546,6 +534,30 @@
   </si>
   <si>
     <t>remark….</t>
+  </si>
+  <si>
+    <t>Nov,2028</t>
+  </si>
+  <si>
+    <t>Project Start Date</t>
+  </si>
+  <si>
+    <t>Agreed rate/sft</t>
+  </si>
+  <si>
+    <t>Material Tolerance Acceptable</t>
+  </si>
+  <si>
+    <t>Central IKON2</t>
+  </si>
+  <si>
+    <t>Rs. 5,00,00,000</t>
+  </si>
+  <si>
+    <t>Feb,2029</t>
+  </si>
+  <si>
+    <t>Jan,2025</t>
   </si>
 </sst>
 </file>
@@ -557,7 +569,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * &quot;-&quot;???_ ;_ @_ "/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -653,8 +665,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -702,6 +739,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -833,7 +882,7 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -922,6 +971,23 @@
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -945,6 +1011,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1299,8 +1374,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K81"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K83"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="3" width="28" customWidth="1"/>
@@ -1309,1412 +1384,1445 @@
     <col min="9" max="9" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:11" ht="36" customHeight="1">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="40"/>
-    </row>
-    <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="50"/>
+    </row>
+    <row r="2" spans="1:11" ht="18" customHeight="1">
+      <c r="A2" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="31"/>
-    </row>
-    <row r="3" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="38"/>
+    </row>
+    <row r="3" spans="1:11" ht="21.95" customHeight="1">
+      <c r="A3" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="31"/>
-    </row>
-    <row r="4" spans="1:11" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="38"/>
+    </row>
+    <row r="4" spans="1:11" ht="23.1" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>107</v>
+        <v>171</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="29">
-        <v>2524471</v>
-      </c>
-      <c r="F4" s="30"/>
-      <c r="G4" s="31"/>
-    </row>
-    <row r="5" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E4" s="36">
+        <v>25200000</v>
+      </c>
+      <c r="F4" s="37"/>
+      <c r="G4" s="38"/>
+    </row>
+    <row r="5" spans="1:11" ht="27.6" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="41" t="s">
-        <v>144</v>
-      </c>
-      <c r="F5" s="30"/>
-      <c r="G5" s="31"/>
-    </row>
-    <row r="6" spans="1:11" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E5" s="51" t="s">
+        <v>141</v>
+      </c>
+      <c r="F5" s="37"/>
+      <c r="G5" s="38"/>
+    </row>
+    <row r="6" spans="1:11" ht="30.95" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="F6" s="41"/>
+      <c r="G6" s="42"/>
+    </row>
+    <row r="7" spans="1:11" ht="30.95" customHeight="1">
+      <c r="A7" s="29"/>
+      <c r="B7" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="E7" s="45">
+        <v>3500</v>
+      </c>
+      <c r="F7" s="46"/>
+      <c r="G7" s="47"/>
+    </row>
+    <row r="8" spans="1:11" ht="29.45" customHeight="1">
+      <c r="A8" s="1"/>
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="36" t="s">
+        <v>167</v>
+      </c>
+      <c r="F8" s="37"/>
+      <c r="G8" s="38"/>
+    </row>
+    <row r="9" spans="1:11" ht="29.45" customHeight="1">
+      <c r="A9" s="1"/>
+      <c r="B9" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D9" s="23"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="38"/>
+    </row>
+    <row r="10" spans="1:11" ht="21.95" customHeight="1">
+      <c r="A10" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="37"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="38"/>
+    </row>
+    <row r="11" spans="1:11" ht="25.5" customHeight="1">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="F6" s="34"/>
-      <c r="G6" s="35"/>
-    </row>
-    <row r="7" spans="1:11" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="G11" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="18" customHeight="1">
+      <c r="A12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" s="14"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+    </row>
+    <row r="13" spans="1:11" ht="18" customHeight="1">
+      <c r="A13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="29" t="s">
-        <v>165</v>
-      </c>
-      <c r="F7" s="30"/>
-      <c r="G7" s="31"/>
-    </row>
-    <row r="8" spans="1:11" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="31"/>
-    </row>
-    <row r="9" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="30"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="31"/>
-    </row>
-    <row r="10" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="D13" s="16">
+        <v>10820.548000000001</v>
+      </c>
+      <c r="E13" s="16">
+        <v>8.36</v>
+      </c>
+      <c r="F13" s="16">
+        <v>90556.619000000006</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="I13" s="27"/>
+      <c r="K13" s="27"/>
+    </row>
+    <row r="14" spans="1:11" ht="18" customHeight="1">
+      <c r="A14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="18"/>
+    </row>
+    <row r="15" spans="1:11" ht="18" customHeight="1">
+      <c r="A15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-    </row>
-    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="12" t="s">
+      <c r="D15" s="19"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+    </row>
+    <row r="16" spans="1:11" ht="18" customHeight="1">
+      <c r="A16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="16">
-        <v>10820.548000000001</v>
-      </c>
-      <c r="E12" s="16">
-        <v>8.36</v>
-      </c>
-      <c r="F12" s="16">
-        <v>90556.619000000006</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="I12" s="27"/>
-      <c r="K12" s="27"/>
-    </row>
-    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="18"/>
-    </row>
-    <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="D14" s="19"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-    </row>
-    <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="D15" s="16">
+      <c r="D16" s="16">
         <v>313.2</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E16" s="16">
         <v>6.45</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F16" s="16">
         <v>2022.951</v>
       </c>
-      <c r="G15" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="I15" s="28"/>
-    </row>
-    <row r="16" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="32" t="s">
+      <c r="G16" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="I16" s="28"/>
+    </row>
+    <row r="17" spans="1:7" ht="21.95" customHeight="1">
+      <c r="A17" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="37"/>
-    </row>
-    <row r="17" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="37"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="44"/>
+    </row>
+    <row r="18" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A18" s="4"/>
+      <c r="B18" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E18" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F18" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G18" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+    <row r="19" spans="1:7" ht="33.6" customHeight="1">
+      <c r="A19" s="6">
         <v>1</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B19" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
-        <v>2</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>163</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="32.450000000000003" customHeight="1">
+      <c r="A20" s="6">
+        <v>2</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="F19" s="26" t="s">
+      <c r="F20" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="32.450000000000003" customHeight="1">
+      <c r="A21" s="6">
+        <v>3</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F21" s="26" t="s">
         <v>159</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
-        <v>3</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="F20" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+      <c r="G21" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="36.6" customHeight="1">
+      <c r="A22" s="6">
         <v>4</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B22" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
-        <v>5</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>36</v>
-      </c>
       <c r="C22" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="18" customHeight="1">
       <c r="A23" s="6">
-        <v>6</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="18" customHeight="1">
+      <c r="A24" s="6">
+        <v>6</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="21.95" customHeight="1">
+      <c r="A25" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="38"/>
+    </row>
+    <row r="26" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A26" s="4"/>
+      <c r="B26" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+    </row>
+    <row r="27" spans="1:7" ht="18" customHeight="1">
+      <c r="A27" s="29">
+        <v>1</v>
+      </c>
+      <c r="B27" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" s="29">
+        <v>5600</v>
+      </c>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+    </row>
+    <row r="28" spans="1:7" ht="18" customHeight="1">
+      <c r="A28" s="29">
+        <v>2</v>
+      </c>
+      <c r="B28" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" s="29">
+        <v>0.06</v>
+      </c>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+    </row>
+    <row r="29" spans="1:7" ht="18" customHeight="1">
+      <c r="A29" s="6">
+        <v>3</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D29" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="38"/>
+    </row>
+    <row r="30" spans="1:7" ht="18" customHeight="1">
+      <c r="A30" s="6">
+        <v>4</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="38"/>
+    </row>
+    <row r="31" spans="1:7" ht="44.1" customHeight="1">
+      <c r="A31" s="6">
+        <v>5</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="E31" s="37"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="38"/>
+    </row>
+    <row r="32" spans="1:7" ht="18" customHeight="1">
+      <c r="A32" s="6">
+        <v>6</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="E32" s="37"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="38"/>
+    </row>
+    <row r="33" spans="1:7" ht="18" customHeight="1">
+      <c r="A33" s="32">
+        <v>7</v>
+      </c>
+      <c r="B33" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="D33" s="29">
+        <v>200</v>
+      </c>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="35"/>
+    </row>
+    <row r="34" spans="1:7" ht="18" customHeight="1">
+      <c r="A34" s="6">
+        <v>7</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="38"/>
+    </row>
+    <row r="35" spans="1:7" ht="18" customHeight="1">
+      <c r="A35" s="6">
+        <v>8</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D35" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E35" s="37"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="38"/>
+    </row>
+    <row r="36" spans="1:7" ht="21.95" customHeight="1">
+      <c r="A36" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="37"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="38"/>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="4"/>
+      <c r="B37" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+    </row>
+    <row r="38" spans="1:7" ht="27.6" customHeight="1">
+      <c r="A38" s="6">
+        <v>1</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E38" s="37"/>
+      <c r="F38" s="37"/>
+      <c r="G38" s="38"/>
+    </row>
+    <row r="39" spans="1:7" ht="26.1" customHeight="1">
+      <c r="A39" s="6">
+        <v>2</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D39" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E39" s="37"/>
+      <c r="F39" s="37"/>
+      <c r="G39" s="38"/>
+    </row>
+    <row r="40" spans="1:7" ht="26.45" customHeight="1">
+      <c r="A40" s="6">
+        <v>3</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D40" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="E40" s="37"/>
+      <c r="F40" s="37"/>
+      <c r="G40" s="38"/>
+    </row>
+    <row r="41" spans="1:7" ht="24.95" customHeight="1">
+      <c r="A41" s="6">
+        <v>4</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D41" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E41" s="37"/>
+      <c r="F41" s="37"/>
+      <c r="G41" s="38"/>
+    </row>
+    <row r="42" spans="1:7" ht="26.45" customHeight="1">
+      <c r="A42" s="6">
+        <v>5</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D42" s="36" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="31"/>
-    </row>
-    <row r="25" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
-      <c r="B25" s="5" t="s">
+      <c r="E42" s="37"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="38"/>
+    </row>
+    <row r="43" spans="1:7" ht="18" customHeight="1">
+      <c r="A43" s="6">
+        <v>6</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D43" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E43" s="37"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="38"/>
+    </row>
+    <row r="44" spans="1:7" ht="18" customHeight="1">
+      <c r="A44" s="6">
+        <v>7</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D44" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="38"/>
+    </row>
+    <row r="45" spans="1:7" ht="18" customHeight="1">
+      <c r="A45" s="6">
+        <v>8</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D45" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E45" s="37"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="38"/>
+    </row>
+    <row r="46" spans="1:7" ht="18" customHeight="1">
+      <c r="A46" s="6">
+        <v>9</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D46" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E46" s="37"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="38"/>
+    </row>
+    <row r="47" spans="1:7" ht="18" customHeight="1">
+      <c r="A47" s="6">
+        <v>10</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D47" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="E47" s="37"/>
+      <c r="F47" s="37"/>
+      <c r="G47" s="38"/>
+    </row>
+    <row r="48" spans="1:7" ht="21.95" customHeight="1">
+      <c r="A48" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48" s="37"/>
+      <c r="C48" s="37"/>
+      <c r="D48" s="37"/>
+      <c r="E48" s="37"/>
+      <c r="F48" s="37"/>
+      <c r="G48" s="38"/>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="4"/>
+      <c r="B49" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" s="5" t="s">
+      <c r="C49" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+    </row>
+    <row r="50" spans="1:7" ht="18" customHeight="1">
+      <c r="A50" s="6">
+        <v>1</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D50" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E50" s="37"/>
+      <c r="F50" s="37"/>
+      <c r="G50" s="38"/>
+    </row>
+    <row r="51" spans="1:7" ht="18" customHeight="1">
+      <c r="A51" s="6">
+        <v>2</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D51" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="E51" s="37"/>
+      <c r="F51" s="37"/>
+      <c r="G51" s="38"/>
+    </row>
+    <row r="52" spans="1:7" ht="18" customHeight="1">
+      <c r="A52" s="6">
+        <v>3</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D52" s="52" t="s">
+        <v>145</v>
+      </c>
+      <c r="E52" s="37"/>
+      <c r="F52" s="37"/>
+      <c r="G52" s="38"/>
+    </row>
+    <row r="53" spans="1:7" ht="18" customHeight="1">
+      <c r="A53" s="6">
+        <v>4</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D53" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E53" s="37"/>
+      <c r="F53" s="37"/>
+      <c r="G53" s="38"/>
+    </row>
+    <row r="54" spans="1:7" ht="18" customHeight="1">
+      <c r="A54" s="6">
+        <v>5</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D54" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="E54" s="37"/>
+      <c r="F54" s="37"/>
+      <c r="G54" s="38"/>
+    </row>
+    <row r="55" spans="1:7" ht="31.5" customHeight="1">
+      <c r="A55" s="6">
+        <v>6</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D55" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E55" s="37"/>
+      <c r="F55" s="37"/>
+      <c r="G55" s="38"/>
+    </row>
+    <row r="56" spans="1:7" ht="31.5" customHeight="1">
+      <c r="A56" s="6">
+        <v>7</v>
+      </c>
+      <c r="B56" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="C56" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="D56" s="53" t="s">
+        <v>166</v>
+      </c>
+      <c r="E56" s="53"/>
+      <c r="F56" s="53"/>
+      <c r="G56" s="54"/>
+    </row>
+    <row r="57" spans="1:7" ht="21.95" customHeight="1">
+      <c r="A57" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B57" s="37"/>
+      <c r="C57" s="43"/>
+      <c r="D57" s="37"/>
+      <c r="E57" s="37"/>
+      <c r="F57" s="37"/>
+      <c r="G57" s="38"/>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="4"/>
+      <c r="B58" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
+    </row>
+    <row r="59" spans="1:7" ht="29.45" customHeight="1">
+      <c r="A59" s="6">
+        <v>1</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D59" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="E59" s="37"/>
+      <c r="F59" s="37"/>
+      <c r="G59" s="38"/>
+    </row>
+    <row r="60" spans="1:7" ht="29.1" customHeight="1">
+      <c r="A60" s="6">
+        <v>2</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C60" s="8">
+        <v>2</v>
+      </c>
+      <c r="D60" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E60" s="37"/>
+      <c r="F60" s="37"/>
+      <c r="G60" s="38"/>
+    </row>
+    <row r="61" spans="1:7" ht="18" customHeight="1">
+      <c r="A61" s="6">
+        <v>3</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="D61" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E61" s="37"/>
+      <c r="F61" s="37"/>
+      <c r="G61" s="38"/>
+    </row>
+    <row r="62" spans="1:7" ht="33.950000000000003" customHeight="1">
+      <c r="A62" s="6">
+        <v>4</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D62" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="E62" s="37"/>
+      <c r="F62" s="37"/>
+      <c r="G62" s="38"/>
+    </row>
+    <row r="63" spans="1:7" ht="27.6" customHeight="1">
+      <c r="A63" s="6">
+        <v>5</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D63" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E63" s="37"/>
+      <c r="F63" s="37"/>
+      <c r="G63" s="38"/>
+    </row>
+    <row r="64" spans="1:7" ht="21.95" customHeight="1">
+      <c r="A64" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="B64" s="37"/>
+      <c r="C64" s="37"/>
+      <c r="D64" s="37"/>
+      <c r="E64" s="37"/>
+      <c r="F64" s="37"/>
+      <c r="G64" s="38"/>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="4"/>
+      <c r="B65" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D65" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+    </row>
+    <row r="66" spans="1:7" ht="18" customHeight="1">
+      <c r="A66" s="6">
         <v>1</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="31"/>
-    </row>
-    <row r="27" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
+      <c r="B66" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D66" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="E66" s="37"/>
+      <c r="F66" s="37"/>
+      <c r="G66" s="38"/>
+    </row>
+    <row r="67" spans="1:7" ht="18" customHeight="1">
+      <c r="A67" s="6">
         <v>2</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D27" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="31"/>
-    </row>
-    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
+      <c r="B67" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D67" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="E67" s="37"/>
+      <c r="F67" s="37"/>
+      <c r="G67" s="38"/>
+    </row>
+    <row r="68" spans="1:7" ht="21.95" customHeight="1">
+      <c r="A68" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="B68" s="37"/>
+      <c r="C68" s="37"/>
+      <c r="D68" s="37"/>
+      <c r="E68" s="37"/>
+      <c r="F68" s="37"/>
+      <c r="G68" s="38"/>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" s="4"/>
+      <c r="B69" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
+    </row>
+    <row r="70" spans="1:7" ht="18" customHeight="1">
+      <c r="A70" s="6">
+        <v>1</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C70" s="3">
+        <v>10</v>
+      </c>
+      <c r="D70" s="57"/>
+      <c r="E70" s="58"/>
+      <c r="F70" s="58"/>
+      <c r="G70" s="59"/>
+    </row>
+    <row r="71" spans="1:7" ht="18" customHeight="1">
+      <c r="A71" s="6">
+        <v>2</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C71" s="3">
+        <v>2</v>
+      </c>
+      <c r="D71" s="57"/>
+      <c r="E71" s="58"/>
+      <c r="F71" s="58"/>
+      <c r="G71" s="59"/>
+    </row>
+    <row r="72" spans="1:7" ht="21.95" customHeight="1">
+      <c r="A72" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="B72" s="37"/>
+      <c r="C72" s="37"/>
+      <c r="D72" s="37"/>
+      <c r="E72" s="37"/>
+      <c r="F72" s="37"/>
+      <c r="G72" s="38"/>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="4"/>
+      <c r="B73" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+    </row>
+    <row r="74" spans="1:7" ht="18" customHeight="1">
+      <c r="A74" s="6">
+        <v>1</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D74" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E74" s="37"/>
+      <c r="F74" s="37"/>
+      <c r="G74" s="38"/>
+    </row>
+    <row r="75" spans="1:7" ht="18" customHeight="1">
+      <c r="A75" s="6">
+        <v>2</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C75" s="8">
+        <v>1</v>
+      </c>
+      <c r="D75" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E75" s="37"/>
+      <c r="F75" s="37"/>
+      <c r="G75" s="38"/>
+    </row>
+    <row r="76" spans="1:7" ht="18" customHeight="1">
+      <c r="A76" s="6">
         <v>3</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D28" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="31"/>
-    </row>
-    <row r="29" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
+      <c r="B76" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D76" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E76" s="37"/>
+      <c r="F76" s="37"/>
+      <c r="G76" s="38"/>
+    </row>
+    <row r="77" spans="1:7" ht="18" customHeight="1">
+      <c r="A77" s="6">
         <v>4</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" s="8" t="s">
+      <c r="B77" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D29" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="31"/>
-    </row>
-    <row r="30" spans="1:7" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
+      <c r="D77" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E77" s="37"/>
+      <c r="F77" s="37"/>
+      <c r="G77" s="38"/>
+    </row>
+    <row r="78" spans="1:7" ht="18" customHeight="1">
+      <c r="A78" s="6">
         <v>5</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D30" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="31"/>
-    </row>
-    <row r="31" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
-        <v>6</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D31" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="31"/>
-    </row>
-    <row r="32" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
-        <v>7</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="D32" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="31"/>
-    </row>
-    <row r="33" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
-        <v>8</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D33" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="31"/>
-    </row>
-    <row r="34" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="31"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="4"/>
-      <c r="B35" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-    </row>
-    <row r="36" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
-        <v>1</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D36" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="31"/>
-    </row>
-    <row r="37" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="6">
-        <v>2</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D37" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="31"/>
-    </row>
-    <row r="38" spans="1:7" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
-        <v>3</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="D38" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="31"/>
-    </row>
-    <row r="39" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="6">
-        <v>4</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D39" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="31"/>
-    </row>
-    <row r="40" spans="1:7" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="6">
-        <v>5</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C40" s="3" t="s">
+      <c r="B78" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D40" s="29" t="s">
-        <v>146</v>
-      </c>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="31"/>
-    </row>
-    <row r="41" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="6">
-        <v>6</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D41" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E41" s="30"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="31"/>
-    </row>
-    <row r="42" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="6">
-        <v>7</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D42" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="31"/>
-    </row>
-    <row r="43" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="6">
-        <v>8</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="D43" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="31"/>
-    </row>
-    <row r="44" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="6">
-        <v>9</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D44" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="31"/>
-    </row>
-    <row r="45" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="6">
-        <v>10</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D45" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="E45" s="30"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="31"/>
-    </row>
-    <row r="46" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="31"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="4"/>
-      <c r="B47" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-    </row>
-    <row r="48" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="6">
-        <v>1</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D48" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E48" s="30"/>
-      <c r="F48" s="30"/>
-      <c r="G48" s="31"/>
-    </row>
-    <row r="49" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="6">
-        <v>2</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="D49" s="42" t="s">
-        <v>130</v>
-      </c>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="31"/>
-    </row>
-    <row r="50" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="6">
-        <v>3</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D50" s="42" t="s">
-        <v>148</v>
-      </c>
-      <c r="E50" s="30"/>
-      <c r="F50" s="30"/>
-      <c r="G50" s="31"/>
-    </row>
-    <row r="51" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="6">
-        <v>4</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="D51" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E51" s="30"/>
-      <c r="F51" s="30"/>
-      <c r="G51" s="31"/>
-    </row>
-    <row r="52" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="6">
-        <v>5</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D52" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="31"/>
-    </row>
-    <row r="53" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="6">
-        <v>6</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D53" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E53" s="30"/>
-      <c r="F53" s="30"/>
-      <c r="G53" s="31"/>
-    </row>
-    <row r="54" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="6">
-        <v>7</v>
-      </c>
-      <c r="B54" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="C54" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="D54" s="43" t="s">
-        <v>170</v>
-      </c>
-      <c r="E54" s="43"/>
-      <c r="F54" s="43"/>
-      <c r="G54" s="44"/>
-    </row>
-    <row r="55" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="B55" s="30"/>
-      <c r="C55" s="36"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
-      <c r="G55" s="31"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="4"/>
-      <c r="B56" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
-    </row>
-    <row r="57" spans="1:7" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="6">
-        <v>1</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D57" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="E57" s="30"/>
-      <c r="F57" s="30"/>
-      <c r="G57" s="31"/>
-    </row>
-    <row r="58" spans="1:7" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="6">
-        <v>2</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C58" s="8">
-        <v>2</v>
-      </c>
-      <c r="D58" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
-      <c r="G58" s="31"/>
-    </row>
-    <row r="59" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="6">
-        <v>3</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C59" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="D59" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E59" s="30"/>
-      <c r="F59" s="30"/>
-      <c r="G59" s="31"/>
-    </row>
-    <row r="60" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="6">
-        <v>4</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D60" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="E60" s="30"/>
-      <c r="F60" s="30"/>
-      <c r="G60" s="31"/>
-    </row>
-    <row r="61" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="6">
-        <v>5</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D61" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E61" s="30"/>
-      <c r="F61" s="30"/>
-      <c r="G61" s="31"/>
-    </row>
-    <row r="62" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="32" t="s">
-        <v>80</v>
-      </c>
-      <c r="B62" s="30"/>
-      <c r="C62" s="30"/>
-      <c r="D62" s="30"/>
-      <c r="E62" s="30"/>
-      <c r="F62" s="30"/>
-      <c r="G62" s="31"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="4"/>
-      <c r="B63" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-    </row>
-    <row r="64" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="6">
-        <v>1</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D64" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="E64" s="30"/>
-      <c r="F64" s="30"/>
-      <c r="G64" s="31"/>
-    </row>
-    <row r="65" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="6">
-        <v>2</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D65" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="E65" s="30"/>
-      <c r="F65" s="30"/>
-      <c r="G65" s="31"/>
-    </row>
-    <row r="66" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="B66" s="30"/>
-      <c r="C66" s="30"/>
-      <c r="D66" s="30"/>
-      <c r="E66" s="30"/>
-      <c r="F66" s="30"/>
-      <c r="G66" s="31"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="4"/>
-      <c r="B67" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
-    </row>
-    <row r="68" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="6">
-        <v>1</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C68" s="3">
-        <v>10</v>
-      </c>
-      <c r="D68" s="47"/>
-      <c r="E68" s="48"/>
-      <c r="F68" s="48"/>
-      <c r="G68" s="49"/>
-    </row>
-    <row r="69" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="6">
-        <v>2</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C69" s="3">
-        <v>2</v>
-      </c>
-      <c r="D69" s="47"/>
-      <c r="E69" s="48"/>
-      <c r="F69" s="48"/>
-      <c r="G69" s="49"/>
-    </row>
-    <row r="70" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="32" t="s">
-        <v>91</v>
-      </c>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="31"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="4"/>
-      <c r="B71" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
-    </row>
-    <row r="72" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="6">
-        <v>1</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D72" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E72" s="30"/>
-      <c r="F72" s="30"/>
-      <c r="G72" s="31"/>
-    </row>
-    <row r="73" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="6">
-        <v>2</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C73" s="8">
-        <v>1</v>
-      </c>
-      <c r="D73" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E73" s="30"/>
-      <c r="F73" s="30"/>
-      <c r="G73" s="31"/>
-    </row>
-    <row r="74" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="6">
-        <v>3</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D74" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E74" s="30"/>
-      <c r="F74" s="30"/>
-      <c r="G74" s="31"/>
-    </row>
-    <row r="75" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="6">
-        <v>4</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D75" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E75" s="30"/>
-      <c r="F75" s="30"/>
-      <c r="G75" s="31"/>
-    </row>
-    <row r="76" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="6">
-        <v>5</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D76" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E76" s="30"/>
-      <c r="F76" s="30"/>
-      <c r="G76" s="31"/>
-    </row>
-    <row r="77" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="32" t="s">
+      <c r="D78" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E78" s="37"/>
+      <c r="F78" s="37"/>
+      <c r="G78" s="38"/>
+    </row>
+    <row r="79" spans="1:7" ht="21.95" customHeight="1">
+      <c r="A79" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="B77" s="30"/>
-      <c r="C77" s="30"/>
-      <c r="D77" s="30"/>
-      <c r="E77" s="30"/>
-      <c r="F77" s="30"/>
-      <c r="G77" s="31"/>
-    </row>
-    <row r="78" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="1"/>
-      <c r="B78" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E78" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="F78" s="30"/>
-      <c r="G78" s="31"/>
-    </row>
-    <row r="79" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="1"/>
-      <c r="B79" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E79" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="F79" s="30"/>
-      <c r="G79" s="31"/>
-    </row>
-    <row r="80" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="37"/>
+      <c r="C79" s="37"/>
+      <c r="D79" s="37"/>
+      <c r="E79" s="37"/>
+      <c r="F79" s="37"/>
+      <c r="G79" s="38"/>
+    </row>
+    <row r="80" spans="1:7" ht="21.95" customHeight="1">
       <c r="A80" s="1"/>
       <c r="B80" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E80" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="F80" s="37"/>
+      <c r="G80" s="38"/>
+    </row>
+    <row r="81" spans="1:7" ht="21.95" customHeight="1">
+      <c r="A81" s="1"/>
+      <c r="B81" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E81" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="F81" s="37"/>
+      <c r="G81" s="38"/>
+    </row>
+    <row r="82" spans="1:7" ht="21.95" customHeight="1">
+      <c r="A82" s="1"/>
+      <c r="B82" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C80" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="D80" s="2"/>
-      <c r="E80" s="29"/>
-      <c r="F80" s="30"/>
-      <c r="G80" s="31"/>
-    </row>
-    <row r="81" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="46" t="s">
+      <c r="C82" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D82" s="2"/>
+      <c r="E82" s="36"/>
+      <c r="F82" s="37"/>
+      <c r="G82" s="38"/>
+    </row>
+    <row r="83" spans="1:7" ht="15.95" customHeight="1">
+      <c r="A83" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="B81" s="30"/>
-      <c r="C81" s="30"/>
-      <c r="D81" s="30"/>
-      <c r="E81" s="30"/>
-      <c r="F81" s="30"/>
-      <c r="G81" s="31"/>
+      <c r="B83" s="37"/>
+      <c r="C83" s="37"/>
+      <c r="D83" s="37"/>
+      <c r="E83" s="37"/>
+      <c r="F83" s="37"/>
+      <c r="G83" s="38"/>
     </row>
   </sheetData>
-  <mergeCells count="61">
-    <mergeCell ref="E79:G79"/>
-    <mergeCell ref="D48:G48"/>
-    <mergeCell ref="D42:G42"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="D65:G65"/>
+  <mergeCells count="60">
+    <mergeCell ref="E81:G81"/>
+    <mergeCell ref="D50:G50"/>
+    <mergeCell ref="D44:G44"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="D67:G67"/>
+    <mergeCell ref="D61:G61"/>
+    <mergeCell ref="D76:G76"/>
+    <mergeCell ref="D63:G63"/>
+    <mergeCell ref="D43:G43"/>
+    <mergeCell ref="D70:G70"/>
+    <mergeCell ref="D71:G71"/>
+    <mergeCell ref="D78:G78"/>
+    <mergeCell ref="D55:G55"/>
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="D60:G60"/>
+    <mergeCell ref="A83:G83"/>
+    <mergeCell ref="D53:G53"/>
+    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="D75:G75"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="D66:G66"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="D51:G51"/>
+    <mergeCell ref="D77:G77"/>
+    <mergeCell ref="E82:G82"/>
     <mergeCell ref="D59:G59"/>
-    <mergeCell ref="D74:G74"/>
-    <mergeCell ref="D61:G61"/>
-    <mergeCell ref="D41:G41"/>
-    <mergeCell ref="D68:G68"/>
-    <mergeCell ref="D69:G69"/>
-    <mergeCell ref="D76:G76"/>
-    <mergeCell ref="D53:G53"/>
-    <mergeCell ref="A66:G66"/>
-    <mergeCell ref="A55:G55"/>
-    <mergeCell ref="D58:G58"/>
-    <mergeCell ref="A81:G81"/>
-    <mergeCell ref="D51:G51"/>
-    <mergeCell ref="D60:G60"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="D73:G73"/>
-    <mergeCell ref="D43:G43"/>
-    <mergeCell ref="D50:G50"/>
-    <mergeCell ref="D64:G64"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="D49:G49"/>
-    <mergeCell ref="D75:G75"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="D39:G39"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D40:G40"/>
     <mergeCell ref="E80:G80"/>
-    <mergeCell ref="D57:G57"/>
-    <mergeCell ref="A46:G46"/>
-    <mergeCell ref="A70:G70"/>
-    <mergeCell ref="D37:G37"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="D38:G38"/>
-    <mergeCell ref="E78:G78"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="E5:G5"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="D72:G72"/>
-    <mergeCell ref="D36:G36"/>
-    <mergeCell ref="A62:G62"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="D29:G29"/>
     <mergeCell ref="D54:G54"/>
+    <mergeCell ref="D74:G74"/>
+    <mergeCell ref="D38:G38"/>
+    <mergeCell ref="A64:G64"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="D56:G56"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E4:G4"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D39:G39"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="D44:G44"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="D47:G47"/>
+    <mergeCell ref="D41:G41"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D46:G46"/>
+    <mergeCell ref="A36:G36"/>
     <mergeCell ref="E6:G6"/>
-    <mergeCell ref="D40:G40"/>
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="D34:G34"/>
     <mergeCell ref="E7:G7"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="D26:G26"/>
   </mergeCells>
   <dataValidations count="14">
-    <dataValidation type="list" allowBlank="1" sqref="C64:C65 C57 C26:C27" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C66:C67 C59 C27:C28" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C28" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C29" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Included,Not Included"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C29 C36 C38 C40:C45" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C30 C38 C40 C42:C47" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Received,Not Received"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C30" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C31" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"Agreed &amp; Documented,Not Agreed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C31" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C32" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"Considered,Not Considered"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C33" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C35" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"Applicable,Not Applicable"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C37 C39" xr:uid="{00000000-0002-0000-0000-000008000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C39 C41" xr:uid="{00000000-0002-0000-0000-000008000000}">
       <formula1>"Received,Not Received,Not Applicable"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C48" xr:uid="{00000000-0002-0000-0000-000011000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C50" xr:uid="{00000000-0002-0000-0000-000011000000}">
       <formula1>"Fabricator,Schüco,Client"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C49" xr:uid="{00000000-0002-0000-0000-000012000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C51" xr:uid="{00000000-0002-0000-0000-000012000000}">
       <formula1>"Approved,Not Approved"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C51" xr:uid="{00000000-0002-0000-0000-000013000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C53" xr:uid="{00000000-0002-0000-0000-000013000000}">
       <formula1>"Black,Silver,White,Custom"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C58" xr:uid="{00000000-0002-0000-0000-000015000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C60" xr:uid="{00000000-0002-0000-0000-000015000000}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C60" xr:uid="{00000000-0002-0000-0000-000016000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C62" xr:uid="{00000000-0002-0000-0000-000016000000}">
       <formula1>"Communicated,Not Communicated"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C61" xr:uid="{00000000-0002-0000-0000-000017000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C63" xr:uid="{00000000-0002-0000-0000-000017000000}">
       <formula1>"By Schüco,By Fabricator"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C72" xr:uid="{00000000-0002-0000-0000-00001A000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C74" xr:uid="{00000000-0002-0000-0000-00001A000000}">
       <formula1>"Pre-Construction,Under Construction,Completed"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="E5" r:id="rId1" xr:uid="{9F7967D9-3318-4BEA-9074-12A66730F786}"/>
-    <hyperlink ref="F19" r:id="rId2" xr:uid="{7E11524D-85F4-4476-A1D3-D01037E65D3D}"/>
-    <hyperlink ref="F20" r:id="rId3" xr:uid="{AD107370-77F5-46D9-A6AA-E8119ACDD27C}"/>
+    <hyperlink ref="F20" r:id="rId2" xr:uid="{7E11524D-85F4-4476-A1D3-D01037E65D3D}"/>
+    <hyperlink ref="F21" r:id="rId3" xr:uid="{AD107370-77F5-46D9-A6AA-E8119ACDD27C}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" verticalDpi="0"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId4"/>
 </worksheet>
 </file>